--- a/data/example/Gas_Parameters.xlsx
+++ b/data/example/Gas_Parameters.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felix Auer\Local\Code\LEGO_internal\examples\001_Base_Example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thomas Klatzer\Desktop\Git\LEGO-Pyomo2\data\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37E3DD7-7C1C-4582-935F-36A80692CDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C629A9D4-FE91-41E6-8278-9C57B4C68739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-17544" windowWidth="30936" windowHeight="16776" tabRatio="958" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43560" yWindow="3210" windowWidth="18420" windowHeight="15585" tabRatio="851" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Parameters" sheetId="121" r:id="rId1"/>
+    <sheet name="Gas Parameters" sheetId="121" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="businfo">#REF!</definedName>
@@ -47,44 +47,90 @@
   <customWorkbookViews>
     <customWorkbookView name="Andres Ramos - Vista personalizada" guid="{162D0EED-4A71-4EB6-8FDF-A42498BFDBC9}" autoUpdate="1" mergeInterval="5" onlySync="1" personalView="1" maximized="1" windowWidth="1112" windowHeight="624" tabRatio="506" activeSheetId="1"/>
   </customWorkbookViews>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Short description</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
   <si>
     <t>General</t>
   </si>
   <si>
-    <t>Cost of Hydrogen not served</t>
-  </si>
-  <si>
-    <t>pH2NSCost</t>
-  </si>
-  <si>
-    <t>[€/kg]</t>
-  </si>
-  <si>
-    <t>Sectors of hydrogen demand</t>
-  </si>
-  <si>
-    <t>h2tec</t>
-  </si>
-  <si>
-    <t>H2_electricity</t>
-  </si>
-  <si>
-    <t>[-]</t>
-  </si>
-  <si>
-    <t>Gas - Parameters</t>
+    <t>Yes/No</t>
+  </si>
+  <si>
+    <t>[Yes, No]</t>
+  </si>
+  <si>
+    <t>Source/ typical values</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Format:</t>
+  </si>
+  <si>
+    <t>Parameters Gas</t>
+  </si>
+  <si>
+    <t>v0.0.1</t>
+  </si>
+  <si>
+    <t>pEnableGas</t>
+  </si>
+  <si>
+    <t>Enable Gas</t>
+  </si>
+  <si>
+    <t>pEnableTP</t>
+  </si>
+  <si>
+    <t>Gas Flow</t>
+  </si>
+  <si>
+    <t>Enable transport problem</t>
+  </si>
+  <si>
+    <t>Enable steady-state problem</t>
+  </si>
+  <si>
+    <t>pEnableStSt</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
@@ -154,6 +200,17 @@
       <sz val="14"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="8">
@@ -235,7 +292,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -252,27 +309,48 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
+    <cellStyle name="Ausgabe" xfId="2" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Data" xfId="1" xr:uid="{226E918E-BB32-45FB-8600-16B83FFE7285}"/>
     <cellStyle name="Hervorhebung" xfId="3" xr:uid="{8678E36F-C265-4DFE-9FC6-523CB5A8AE55}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
     <cellStyle name="Normal 2" xfId="4" xr:uid="{18929256-C3F4-489D-8BCE-E323A983834F}"/>
-    <cellStyle name="Output" xfId="2" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0" customBuiltin="1"/>
     <cellStyle name="Standard 2" xfId="5" xr:uid="{5DF4A97E-8529-4A9B-8CDD-1ED3E5DC1118}"/>
     <cellStyle name="Standard 3" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
     <cellStyle name="Standard 4" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
     <dxf>
       <font>
         <b/>
@@ -285,6 +363,20 @@
         <b/>
         <i val="0"/>
         <color rgb="FFB90135"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFB90135"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF4E9C49"/>
       </font>
     </dxf>
     <dxf>
@@ -618,129 +710,149 @@
   <sheetPr>
     <tabColor rgb="FF008080"/>
   </sheetPr>
-  <dimension ref="B1:N13"/>
-  <sheetFormatPr defaultColWidth="10.8984375" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:H12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="51.09765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.8984375" style="1"/>
+    <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="120.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>8</v>
       </c>
+      <c r="E3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="2:14" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="6" t="s">
+    <row r="4" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="12"/>
+    </row>
+    <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>0</v>
       </c>
+      <c r="E5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>3</v>
+    <row r="7" spans="2:8" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7"/>
-      <c r="M7"/>
-      <c r="N7"/>
-    </row>
-    <row r="8" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>5</v>
+    <row r="8" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
-      <c r="M8"/>
-      <c r="N8"/>
     </row>
-    <row r="9" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
+    <row r="9" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="10" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
-      <c r="N10"/>
+    <row r="11" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="11" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-    </row>
-    <row r="12" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
-      <c r="M12"/>
-      <c r="N12"/>
-    </row>
-    <row r="13" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I13"/>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
-      <c r="M13"/>
-      <c r="N13"/>
+    <row r="12" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C5:C6">
-    <cfRule type="cellIs" dxfId="3" priority="67" operator="equal">
+  <conditionalFormatting sqref="C5">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+  <conditionalFormatting sqref="C9">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"No"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="C6" xr:uid="{87C6F772-FD4B-9449-B9E7-DA0FF0A031BB}"/>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="C5 C9 C12" xr:uid="{3037D345-D942-4EE1-9FD6-4C812B603C20}">
+      <formula1>"No, Yes"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
